--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_244_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_244_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.019</v>
+        <v>8.0646</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9618</v>
+        <v>6.0745</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0572</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
         <v>2.0913</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5566</v>
+        <v>1.6021</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1102</v>
+        <v>1.223</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4463</v>
+        <v>0.3791</v>
       </c>
       <c r="V2" t="n">
         <v>1.3558</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9067</v>
+        <v>7.6899</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9675</v>
+        <v>2.5573</v>
       </c>
       <c r="F3" t="n">
-        <v>5.9391</v>
+        <v>5.1326</v>
       </c>
       <c r="G3" t="n">
         <v>0.8505</v>
@@ -688,13 +688,13 @@
         <v>3.9432</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1078</v>
+        <v>1.891</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2284</v>
+        <v>0.8182</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8793</v>
+        <v>1.0728</v>
       </c>
       <c r="V3" t="n">
         <v>2.3969</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9385</v>
+        <v>2.7322</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3161</v>
+        <v>1.407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6224</v>
+        <v>1.3252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1823</v>
+        <v>0.9448</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5809</v>
+        <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3986</v>
+        <v>-0.5052</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4586</v>
+        <v>1.5915</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1713</v>
+        <v>1.2001</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7127</v>
+        <v>0.3914</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2762</v>
+        <v>-0.6468</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5904</v>
+        <v>0.2499</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6859</v>
+        <v>-0.8966</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>3.2473</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>3.2473</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5242</v>
+        <v>-0.1041</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2492</v>
+        <v>-0.1845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.275</v>
+        <v>0.0804</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4559</v>
+        <v>1.7683</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3323</v>
+        <v>0.4608</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1235</v>
+        <v>1.3075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9448</v>
+        <v>0.4533</v>
       </c>
       <c r="H5" t="n">
-        <v>1.45</v>
+        <v>2.3204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5052</v>
+        <v>-1.867</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5915</v>
+        <v>1.354</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2001</v>
+        <v>1.9564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3914</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6468</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2499</v>
+        <v>0.364</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8966</v>
+        <v>-1.2647</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2473</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2473</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3804</v>
+        <v>1.1705</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2592</v>
+        <v>0.586</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1212</v>
+        <v>0.5845</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3558</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4645</v>
+        <v>1.3619</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.011</v>
+        <v>0.7395</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4755</v>
+        <v>0.6224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4533</v>
+        <v>0.1823</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3204</v>
+        <v>1.5809</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.867</v>
+        <v>-1.3986</v>
       </c>
       <c r="J6" t="n">
-        <v>1.354</v>
+        <v>1.4586</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9564</v>
+        <v>2.1713</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.7127</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-1.2762</v>
       </c>
       <c r="N6" t="n">
-        <v>0.364</v>
+        <v>-0.5904</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2647</v>
+        <v>-0.6859</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8667</v>
+        <v>0.9476</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1142</v>
+        <v>0.6726</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.275</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1541</v>
+        <v>-0.3462</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.1994</v>
+        <v>-3.7275</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0453</v>
+        <v>3.3813</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0876</v>
@@ -1000,13 +1000,13 @@
         <v>3.4793</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4876</v>
+        <v>1.2955</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3031</v>
+        <v>0.7749</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1845</v>
+        <v>0.5206</v>
       </c>
       <c r="V7" t="n">
         <v>0.6778999999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8655</v>
+        <v>-0.7131</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4199</v>
+        <v>-2.8921</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4456</v>
+        <v>2.179</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3223</v>
+        <v>0.2926</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1944</v>
+        <v>-0.39</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.5167</v>
+        <v>0.6826</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9641999999999999</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3948</v>
+        <v>-0.2822</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.359</v>
+        <v>1.0539</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3581</v>
+        <v>-0.4791</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2004</v>
+        <v>-0.1078</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1577</v>
+        <v>-0.3713</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.7112</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8448</v>
+        <v>0.2959</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>0.0474</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2473</v>
+        <v>0.2484</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0338</v>
+        <v>-1.4541</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9104</v>
+        <v>-1.1093</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8765</v>
+        <v>-0.3448</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2926</v>
+        <v>-2.3223</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.39</v>
+        <v>1.1944</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6826</v>
+        <v>-3.5167</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7717000000000001</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2822</v>
+        <v>1.3948</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0539</v>
+        <v>-2.359</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4791</v>
+        <v>-1.3581</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1078</v>
+        <v>-0.2004</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3713</v>
+        <v>-1.1577</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>1.1598</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0249</v>
+        <v>-0.4334</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9709</v>
+        <v>-0.2869</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.054</v>
+        <v>-0.1465</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7556</v>
+        <v>-2.7818</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3195</v>
+        <v>-0.2448</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4361</v>
+        <v>-2.5369</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5465</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2245</v>
+        <v>-0.2506</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>-0.2987</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V10" t="n">
         <v>-2.6805</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2101</v>
+        <v>-3.1828</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.423</v>
+        <v>-2.5973</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7871</v>
+        <v>-0.5855</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2675</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7776</v>
+        <v>0.2497</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5975</v>
+        <v>0.2282</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1801</v>
+        <v>0.0215</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8608</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.7655</v>
+        <v>13.1389</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2944999999999989</v>
+        <v>0.6681000000000008</v>
       </c>
       <c r="F12" t="n">
-        <v>12.4707</v>
+        <v>12.4708</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4091</v>
@@ -1390,10 +1390,10 @@
         <v>23.1954</v>
       </c>
       <c r="S12" t="n">
-        <v>6.290700000000002</v>
+        <v>6.664199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2066</v>
+        <v>3.5802</v>
       </c>
       <c r="U12" t="n">
         <v>3.0839</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.104</v>
+        <v>2.4407</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8442</v>
+        <v>3.0801</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7402</v>
+        <v>-0.6394</v>
       </c>
       <c r="G13" t="n">
         <v>2.9908</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4229</v>
+        <v>-1.0862</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7389</v>
+        <v>-0.503</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.674</v>
+        <v>2.0278</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2784</v>
+        <v>2.6323</v>
       </c>
       <c r="F14" t="n">
         <v>-0.6044</v>
@@ -1546,10 +1546,10 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4154</v>
+        <v>-1.0616</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4323</v>
+        <v>-0.0784</v>
       </c>
       <c r="U14" t="n">
         <v>-0.9831</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6584</v>
+        <v>0.3217</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2345</v>
+        <v>-1.4704</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8929</v>
+        <v>1.7921</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0162</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3976</v>
+        <v>-0.7343</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4832</v>
+        <v>-0.7191</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0857</v>
+        <v>-0.0151</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1349</v>
+        <v>0.3023</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2156</v>
+        <v>-0.4515</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3505</v>
+        <v>0.7538</v>
       </c>
       <c r="G16" t="n">
         <v>1.4483</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4216</v>
+        <v>-1.2542</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4086</v>
+        <v>-0.6445</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.013</v>
+        <v>-0.6097</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8197</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4932</v>
+        <v>-0.6277</v>
       </c>
       <c r="E17" t="n">
         <v>0.474</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.1017</v>
       </c>
       <c r="G17" t="n">
         <v>0.3699</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2091</v>
+        <v>0.0747</v>
       </c>
       <c r="T17" t="n">
         <v>0.08260000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1265</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0759</v>
+        <v>-0.8737</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1935</v>
+        <v>0.0424</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8825</v>
+        <v>-0.9161</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5972</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0328</v>
+        <v>-0.8305</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5926</v>
+        <v>-0.6262</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5645</v>
+        <v>-1.5379</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5751</v>
+        <v>-2.9853</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0106</v>
+        <v>1.4475</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9206</v>
@@ -1936,13 +1936,13 @@
         <v>2.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8631</v>
+        <v>-0.8364</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.187</v>
+        <v>-0.5972</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6761</v>
+        <v>-0.2392</v>
       </c>
       <c r="V19" t="n">
         <v>2.5387</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9195</v>
+        <v>-3.1547</v>
       </c>
       <c r="E20" t="n">
         <v>-2.9327</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0132</v>
+        <v>-0.222</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2083</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2473</v>
+        <v>-0.4826</v>
       </c>
       <c r="T20" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2754</v>
+        <v>0.0402</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1129</v>
+        <v>-3.3323</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3108</v>
+        <v>-1.6647</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8021</v>
+        <v>-1.6676</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2262</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1133</v>
+        <v>-0.1061</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6528</v>
+        <v>0.2989</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5395</v>
+        <v>-0.405</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4868</v>
+        <v>-4.0377</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6049</v>
+        <v>-3.354</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1182</v>
+        <v>-0.6837</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4468</v>
+        <v>-0.2201</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3998</v>
+        <v>0.0241</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8466</v>
+        <v>-0.2442</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3188</v>
+        <v>0.1408</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8843</v>
+        <v>0.0672</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5655</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>0.128</v>
+        <v>-0.3609</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2842</v>
+        <v>-0.0431</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4122</v>
+        <v>-0.3178</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.1751</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q22" t="n">
-        <v>-6.0307</v>
+        <v>-3.7112</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0302</v>
+        <v>-0.1966</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1766</v>
+        <v>0.2164</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2068</v>
+        <v>-0.4129</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7886</v>
+        <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6839</v>
+        <v>-4.294</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0002</v>
+        <v>-5.8408</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6837</v>
+        <v>1.5469</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2201</v>
+        <v>0.4468</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0241</v>
+        <v>-0.3998</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2442</v>
+        <v>0.8466</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1408</v>
+        <v>0.3188</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0672</v>
+        <v>0.8843</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0736</v>
+        <v>-0.5655</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3609</v>
+        <v>0.128</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0431</v>
+        <v>-1.2842</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3178</v>
+        <v>1.4122</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4793</v>
+        <v>-4.1751</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7112</v>
+        <v>-6.0307</v>
       </c>
       <c r="R23" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1573</v>
+        <v>0.2229</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5702</v>
+        <v>-0.4125</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4129</v>
+        <v>0.6355</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.7654</v>
+        <v>-12.7655</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.4707</v>
+        <v>-12.4706</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2947000000000002</v>
+        <v>-0.2945999999999998</v>
       </c>
       <c r="G24" t="n">
         <v>2.4091</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.348599999999999</v>
+        <v>-8.348600000000001</v>
       </c>
       <c r="I24" t="n">
         <v>10.7574</v>
       </c>
       <c r="J24" t="n">
-        <v>7.202099999999999</v>
+        <v>7.202099999999998</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7103000000000004</v>
+        <v>-0.7103000000000005</v>
       </c>
       <c r="L24" t="n">
         <v>7.912500000000001</v>
@@ -2317,7 +2317,7 @@
         <v>2.8452</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.278</v>
+        <v>-9.277999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-23.1952</v>
@@ -2326,16 +2326,16 @@
         <v>13.9172</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.290800000000001</v>
+        <v>-6.2909</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.084</v>
+        <v>-3.0839</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.2068</v>
+        <v>-3.2066</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3943</v>
+        <v>0.3943000000000001</v>
       </c>
       <c r="W24" t="n">
         <v>6.6061</v>
